--- a/Icons/ace Colors.xlsx
+++ b/Icons/ace Colors.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20396"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20397"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Natural gas vs. green chemicals\Icons\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Fossil vs. green chemicals\Icons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F42917E-D9B7-4AB2-839D-308320DDBEFE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0705B3-BEF0-448E-9BD8-50F4A5829828}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12228" xr2:uid="{2C07BDD4-A521-4DF7-BD87-0D464734E695}"/>
   </bookViews>
